--- a/lab3/oscillator/range finder.xlsx
+++ b/lab3/oscillator/range finder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pig\Documents\ee251\lab3\oscillator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD24D46F-7542-45B1-A6F8-4D60B0AC2EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023556CF-AD18-483F-BF73-1EA9B3DD7423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8736" yWindow="696" windowWidth="13740" windowHeight="11232" xr2:uid="{01CC5717-1875-4BB2-821A-9A8B42689899}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
     <t>C1 (pF)</t>
   </si>
@@ -44,25 +44,46 @@
     <t>C2 (pF)</t>
   </si>
   <si>
-    <t>L_bot (nH)</t>
-  </si>
-  <si>
-    <t>L_top (nH)</t>
-  </si>
-  <si>
-    <t>fL (MHz)</t>
-  </si>
-  <si>
-    <t>fH(MHz)</t>
-  </si>
-  <si>
-    <t>Ceq (pF)</t>
+    <t>L (nH)</t>
+  </si>
+  <si>
+    <t>f_high (MHz)</t>
+  </si>
+  <si>
+    <t>f_low (MHz)</t>
+  </si>
+  <si>
+    <t>C_eq (pF)</t>
+  </si>
+  <si>
+    <t>low freq</t>
+  </si>
+  <si>
+    <t>high freq</t>
+  </si>
+  <si>
+    <t>Varcap range (pF)</t>
+  </si>
+  <si>
+    <t>Varcap bot (pF)</t>
+  </si>
+  <si>
+    <t>Varcap top (pF)</t>
+  </si>
+  <si>
+    <t>from datasheet</t>
+  </si>
+  <si>
+    <t>Varcaop offset (pF)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="0.0"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -92,8 +113,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -428,75 +451,136 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6449CF9-28C9-46D2-83E3-AF4E570CADDA}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="16.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1">
-        <v>15</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2">
-        <f>B1*4</f>
-        <v>60</v>
-      </c>
-      <c r="C2">
-        <f>B2/B1</f>
-        <v>4</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <f>B1*B2/(B2+B1)</f>
-        <v>12</v>
+        <v>118.7</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>98.7</v>
+        <v>5</v>
+      </c>
+      <c r="B5" s="1">
+        <f>1/((2*PI()*B2*10^6)^2*B1*10^(-9))*10^12</f>
+        <v>17.334634894345463</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>118.7</v>
+      <c r="B6" s="1">
+        <f>1/((2*PI()*B3*10^6)^2*B1*10^(-9))*10^12</f>
+        <v>11.985262940767061</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8">
-        <f>1/((2*PI()*B5*10^(6))^2*B3*10^(-12))*10^9</f>
-        <v>216.68293617931829</v>
+        <v>1</v>
+      </c>
+      <c r="B8" s="2">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <f>1/((2*PI()*B6*10^(6))^2*B3*10^(-12))*10^9</f>
-        <v>149.81578675958826</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B9" s="1">
+        <f>B8*B5/(B8-B5)</f>
+        <v>20.969646565027666</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="1">
+        <f>B8*B6/(B8-B6)</f>
+        <v>13.617336529337255</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B11" s="1"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1">
+        <f>B9-B10</f>
+        <v>7.3523100356904116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1">
+        <f>B14-B12</f>
+        <v>10.647689964309588</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="1">
+        <f>B9-B14</f>
+        <v>2.9696465650276664</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B18" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
